--- a/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
+++ b/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Inventory\Assets\Excel\Equipment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\FPS_Test\Assets\Excel\Equipment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDAD008-E934-4E38-909A-5BC1054361F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E264D15-B27C-4FE0-9993-8168B40BFA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentAbility" sheetId="1" r:id="rId1"/>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -640,7 +640,7 @@
         <v>50</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -815,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -850,7 +850,7 @@
         <v>50</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1025,7 +1025,7 @@
         <v>50</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1095,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1200,7 +1200,7 @@
         <v>50</v>
       </c>
       <c r="K21">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">

--- a/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
+++ b/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\FPS_Test\Assets\Excel\Equipment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E264D15-B27C-4FE0-9993-8168B40BFA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CBF92F-9ADD-40D9-9666-AF3B74F9962E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -491,13 +491,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>

--- a/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
+++ b/FPS_Test/Assets/Excel/Equipment/EquipmentData.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\FPS_Test\Assets\Excel\Equipment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\Equipment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CBF92F-9ADD-40D9-9666-AF3B74F9962E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2567AB0B-EB88-4EF6-B2C1-3EE7A55349C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentAbility" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
